--- a/30_table/01_테스트버전/Table_List_Map.xlsx
+++ b/30_table/01_테스트버전/Table_List_Map.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="217">
   <si>
     <t>작업자</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -674,6 +674,75 @@
   <si>
     <t>Map</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>개발자의 방으로</t>
+  </si>
+  <si>
+    <t>개발자와 대화 1</t>
+  </si>
+  <si>
+    <t>개발자와 대화 2</t>
+  </si>
+  <si>
+    <t>개발자와 대화 3</t>
+  </si>
+  <si>
+    <t>시험 2</t>
+  </si>
+  <si>
+    <t>시험 3</t>
+  </si>
+  <si>
+    <t>개발자와 대화 4</t>
+  </si>
+  <si>
+    <t>list_map_46</t>
+  </si>
+  <si>
+    <t>list_map_47</t>
+  </si>
+  <si>
+    <t>list_map_48</t>
+  </si>
+  <si>
+    <t>list_map_49</t>
+  </si>
+  <si>
+    <t>list_map_50</t>
+  </si>
+  <si>
+    <t>list_map_51</t>
+  </si>
+  <si>
+    <t>list_map_52</t>
+  </si>
+  <si>
+    <t>list_map_53</t>
+  </si>
+  <si>
+    <t>map_s1_006</t>
+  </si>
+  <si>
+    <t>map_s1_007</t>
+  </si>
+  <si>
+    <t>map_s1_008</t>
+  </si>
+  <si>
+    <t>map_s1_009</t>
+  </si>
+  <si>
+    <t>map_s1_010</t>
+  </si>
+  <si>
+    <t>map_s1_011</t>
+  </si>
+  <si>
+    <t>map_s1_012</t>
+  </si>
+  <si>
+    <t>map_s1_005</t>
   </si>
 </sst>
 </file>
@@ -4179,7 +4248,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:J46"/>
+  <dimension ref="A1:J54"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.5" style="35" bestFit="1" customWidth="1"/>
@@ -5664,6 +5733,262 @@
         <v>55</v>
       </c>
       <c r="J46" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A47" s="32">
+        <v>46</v>
+      </c>
+      <c r="B47" s="35" t="s">
+        <v>194</v>
+      </c>
+      <c r="C47" s="32" t="s">
+        <v>201</v>
+      </c>
+      <c r="D47" s="35" t="s">
+        <v>216</v>
+      </c>
+      <c r="E47" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="F47" s="35">
+        <v>50003</v>
+      </c>
+      <c r="G47" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="H47" s="32">
+        <v>0</v>
+      </c>
+      <c r="I47" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="J47" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A48" s="32">
+        <v>47</v>
+      </c>
+      <c r="B48" s="35" t="s">
+        <v>195</v>
+      </c>
+      <c r="C48" s="32" t="s">
+        <v>202</v>
+      </c>
+      <c r="D48" s="35" t="s">
+        <v>209</v>
+      </c>
+      <c r="E48" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="F48" s="35">
+        <v>50045</v>
+      </c>
+      <c r="G48" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="H48" s="32">
+        <v>0</v>
+      </c>
+      <c r="I48" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="J48" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A49" s="32">
+        <v>48</v>
+      </c>
+      <c r="B49" s="35" t="s">
+        <v>196</v>
+      </c>
+      <c r="C49" s="32" t="s">
+        <v>203</v>
+      </c>
+      <c r="D49" s="35" t="s">
+        <v>210</v>
+      </c>
+      <c r="E49" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="F49" s="35">
+        <v>50046</v>
+      </c>
+      <c r="G49" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="H49" s="32">
+        <v>0</v>
+      </c>
+      <c r="I49" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="J49" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A50" s="32">
+        <v>49</v>
+      </c>
+      <c r="B50" s="35" t="s">
+        <v>197</v>
+      </c>
+      <c r="C50" s="32" t="s">
+        <v>204</v>
+      </c>
+      <c r="D50" s="35" t="s">
+        <v>211</v>
+      </c>
+      <c r="E50" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="F50" s="35">
+        <v>50047</v>
+      </c>
+      <c r="G50" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="H50" s="32">
+        <v>0</v>
+      </c>
+      <c r="I50" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="J50" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A51" s="32">
+        <v>50</v>
+      </c>
+      <c r="B51" s="35" t="s">
+        <v>198</v>
+      </c>
+      <c r="C51" s="32" t="s">
+        <v>205</v>
+      </c>
+      <c r="D51" s="35" t="s">
+        <v>212</v>
+      </c>
+      <c r="E51" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="F51" s="35">
+        <v>50048</v>
+      </c>
+      <c r="G51" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="H51" s="32">
+        <v>0</v>
+      </c>
+      <c r="I51" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="J51" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A52" s="32">
+        <v>51</v>
+      </c>
+      <c r="B52" s="35" t="s">
+        <v>199</v>
+      </c>
+      <c r="C52" s="32" t="s">
+        <v>206</v>
+      </c>
+      <c r="D52" s="35" t="s">
+        <v>213</v>
+      </c>
+      <c r="E52" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="F52" s="35">
+        <v>50049</v>
+      </c>
+      <c r="G52" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="H52" s="32">
+        <v>0</v>
+      </c>
+      <c r="I52" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="J52" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A53" s="32">
+        <v>52</v>
+      </c>
+      <c r="B53" s="35" t="s">
+        <v>199</v>
+      </c>
+      <c r="C53" s="32" t="s">
+        <v>207</v>
+      </c>
+      <c r="D53" s="35" t="s">
+        <v>214</v>
+      </c>
+      <c r="E53" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="F53" s="35">
+        <v>50050</v>
+      </c>
+      <c r="G53" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="H53" s="32">
+        <v>0</v>
+      </c>
+      <c r="I53" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="J53" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A54" s="32">
+        <v>53</v>
+      </c>
+      <c r="B54" s="35" t="s">
+        <v>200</v>
+      </c>
+      <c r="C54" s="32" t="s">
+        <v>208</v>
+      </c>
+      <c r="D54" s="35" t="s">
+        <v>215</v>
+      </c>
+      <c r="E54" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="F54" s="35">
+        <v>50051</v>
+      </c>
+      <c r="G54" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="H54" s="32">
+        <v>0</v>
+      </c>
+      <c r="I54" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="J54" s="32">
         <v>0</v>
       </c>
     </row>

--- a/30_table/01_테스트버전/Table_List_Map.xlsx
+++ b/30_table/01_테스트버전/Table_List_Map.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="250">
   <si>
     <t>작업자</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -743,6 +743,107 @@
   </si>
   <si>
     <t>map_s1_005</t>
+  </si>
+  <si>
+    <t>list_map_54</t>
+  </si>
+  <si>
+    <t>list_map_55</t>
+  </si>
+  <si>
+    <t>list_map_56</t>
+  </si>
+  <si>
+    <t>list_map_57</t>
+  </si>
+  <si>
+    <t>list_map_58</t>
+  </si>
+  <si>
+    <t>list_map_59</t>
+  </si>
+  <si>
+    <t>list_map_60</t>
+  </si>
+  <si>
+    <t>list_map_61</t>
+  </si>
+  <si>
+    <t>list_map_62</t>
+  </si>
+  <si>
+    <t>list_map_63</t>
+  </si>
+  <si>
+    <t>list_map_64</t>
+  </si>
+  <si>
+    <t>욕심</t>
+  </si>
+  <si>
+    <t>죽은 자의 동굴  1층</t>
+  </si>
+  <si>
+    <t>좀비 조심</t>
+  </si>
+  <si>
+    <t>박쥐 사냥</t>
+  </si>
+  <si>
+    <t>좀비방</t>
+  </si>
+  <si>
+    <t>숨겨진 방으로</t>
+  </si>
+  <si>
+    <t>보물방</t>
+  </si>
+  <si>
+    <t>동굴 1층</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>믿음</t>
+  </si>
+  <si>
+    <t>만족</t>
+  </si>
+  <si>
+    <t>지하 2층으로</t>
+  </si>
+  <si>
+    <t>map_s4_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>map_s4_002</t>
+  </si>
+  <si>
+    <t>map_s4_003</t>
+  </si>
+  <si>
+    <t>map_s4_004</t>
+  </si>
+  <si>
+    <t>map_s4_005</t>
+  </si>
+  <si>
+    <t>map_s4_006</t>
+  </si>
+  <si>
+    <t>map_s4_007</t>
+  </si>
+  <si>
+    <t>map_s4_008</t>
+  </si>
+  <si>
+    <t>map_s4_009</t>
+  </si>
+  <si>
+    <t>map_s4_010</t>
+  </si>
+  <si>
+    <t>map_s4_011</t>
   </si>
 </sst>
 </file>
@@ -4248,7 +4349,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:J54"/>
+  <dimension ref="A1:J66"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.5" style="35" bestFit="1" customWidth="1"/>
@@ -5991,6 +6092,361 @@
       <c r="J54" s="32">
         <v>0</v>
       </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A55" s="32">
+        <v>54</v>
+      </c>
+      <c r="B55" s="35" t="s">
+        <v>228</v>
+      </c>
+      <c r="C55" s="32" t="s">
+        <v>217</v>
+      </c>
+      <c r="D55" s="32" t="s">
+        <v>239</v>
+      </c>
+      <c r="E55" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="F55" s="35">
+        <v>50038</v>
+      </c>
+      <c r="G55" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="H55" s="32">
+        <v>0</v>
+      </c>
+      <c r="I55" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="J55" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A56" s="32">
+        <v>55</v>
+      </c>
+      <c r="B56" s="35" t="s">
+        <v>229</v>
+      </c>
+      <c r="C56" s="32" t="s">
+        <v>218</v>
+      </c>
+      <c r="D56" s="32" t="s">
+        <v>240</v>
+      </c>
+      <c r="E56" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="F56" s="35">
+        <v>50053</v>
+      </c>
+      <c r="G56" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="H56" s="32">
+        <v>0</v>
+      </c>
+      <c r="I56" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="J56" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A57" s="32">
+        <v>56</v>
+      </c>
+      <c r="B57" s="35" t="s">
+        <v>230</v>
+      </c>
+      <c r="C57" s="32" t="s">
+        <v>219</v>
+      </c>
+      <c r="D57" s="32" t="s">
+        <v>241</v>
+      </c>
+      <c r="E57" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="F57" s="32">
+        <v>50054</v>
+      </c>
+      <c r="G57" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="H57" s="32">
+        <v>0</v>
+      </c>
+      <c r="I57" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="J57" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A58" s="32">
+        <v>57</v>
+      </c>
+      <c r="B58" s="35" t="s">
+        <v>231</v>
+      </c>
+      <c r="C58" s="32" t="s">
+        <v>220</v>
+      </c>
+      <c r="D58" s="32" t="s">
+        <v>242</v>
+      </c>
+      <c r="E58" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="F58" s="32">
+        <v>50055</v>
+      </c>
+      <c r="G58" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="H58" s="32">
+        <v>0</v>
+      </c>
+      <c r="I58" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="J58" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A59" s="32">
+        <v>58</v>
+      </c>
+      <c r="B59" s="35" t="s">
+        <v>232</v>
+      </c>
+      <c r="C59" s="32" t="s">
+        <v>221</v>
+      </c>
+      <c r="D59" s="32" t="s">
+        <v>243</v>
+      </c>
+      <c r="E59" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="F59" s="32">
+        <v>50056</v>
+      </c>
+      <c r="G59" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="H59" s="32">
+        <v>0</v>
+      </c>
+      <c r="I59" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="J59" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A60" s="32">
+        <v>59</v>
+      </c>
+      <c r="B60" s="35" t="s">
+        <v>233</v>
+      </c>
+      <c r="C60" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="D60" s="32" t="s">
+        <v>244</v>
+      </c>
+      <c r="E60" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="F60" s="32">
+        <v>50057</v>
+      </c>
+      <c r="G60" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="H60" s="32">
+        <v>0</v>
+      </c>
+      <c r="I60" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="J60" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A61" s="32">
+        <v>60</v>
+      </c>
+      <c r="B61" s="35" t="s">
+        <v>234</v>
+      </c>
+      <c r="C61" s="32" t="s">
+        <v>223</v>
+      </c>
+      <c r="D61" s="32" t="s">
+        <v>245</v>
+      </c>
+      <c r="E61" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="F61" s="32">
+        <v>50058</v>
+      </c>
+      <c r="G61" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="H61" s="32">
+        <v>0</v>
+      </c>
+      <c r="I61" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="J61" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A62" s="32">
+        <v>61</v>
+      </c>
+      <c r="B62" s="35" t="s">
+        <v>235</v>
+      </c>
+      <c r="C62" s="32" t="s">
+        <v>224</v>
+      </c>
+      <c r="D62" s="32" t="s">
+        <v>246</v>
+      </c>
+      <c r="E62" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="F62" s="32">
+        <v>50057</v>
+      </c>
+      <c r="G62" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="H62" s="32">
+        <v>0</v>
+      </c>
+      <c r="I62" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="J62" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A63" s="32">
+        <v>62</v>
+      </c>
+      <c r="B63" s="35" t="s">
+        <v>236</v>
+      </c>
+      <c r="C63" s="32" t="s">
+        <v>225</v>
+      </c>
+      <c r="D63" s="32" t="s">
+        <v>247</v>
+      </c>
+      <c r="E63" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="F63" s="32">
+        <v>50060</v>
+      </c>
+      <c r="G63" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="H63" s="32">
+        <v>0</v>
+      </c>
+      <c r="I63" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="J63" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A64" s="32">
+        <v>63</v>
+      </c>
+      <c r="B64" s="35" t="s">
+        <v>237</v>
+      </c>
+      <c r="C64" s="32" t="s">
+        <v>226</v>
+      </c>
+      <c r="D64" s="32" t="s">
+        <v>248</v>
+      </c>
+      <c r="E64" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="F64" s="32">
+        <v>50061</v>
+      </c>
+      <c r="G64" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="H64" s="32">
+        <v>0</v>
+      </c>
+      <c r="I64" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="J64" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A65" s="32">
+        <v>64</v>
+      </c>
+      <c r="B65" s="35" t="s">
+        <v>238</v>
+      </c>
+      <c r="C65" s="32" t="s">
+        <v>227</v>
+      </c>
+      <c r="D65" s="32" t="s">
+        <v>249</v>
+      </c>
+      <c r="E65" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="F65" s="32">
+        <v>50062</v>
+      </c>
+      <c r="G65" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="H65" s="32">
+        <v>0</v>
+      </c>
+      <c r="I65" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="J65" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="F66" s="32"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:H2"/>

--- a/30_table/01_테스트버전/Table_List_Map.xlsx
+++ b/30_table/01_테스트버전/Table_List_Map.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr codeName="현재_통합_문서" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="-15" yWindow="-15" windowWidth="16230" windowHeight="25245" activeTab="2"/>
+    <workbookView xWindow="-15" yWindow="45" windowWidth="16230" windowHeight="25185" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="DOC History" sheetId="6" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="298">
   <si>
     <t>작업자</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -844,6 +844,152 @@
   </si>
   <si>
     <t>map_s4_011</t>
+  </si>
+  <si>
+    <t>죽은 자의 동굴 2층</t>
+  </si>
+  <si>
+    <t>구울 조심</t>
+  </si>
+  <si>
+    <t>함정 1</t>
+  </si>
+  <si>
+    <t>구울방</t>
+  </si>
+  <si>
+    <t>함정 2</t>
+  </si>
+  <si>
+    <t>라미를 찾아서</t>
+  </si>
+  <si>
+    <t>라미의 부탁</t>
+  </si>
+  <si>
+    <t>좀비의 영혼</t>
+  </si>
+  <si>
+    <t>라미에게 줄 선물</t>
+  </si>
+  <si>
+    <t>라미의 조언</t>
+  </si>
+  <si>
+    <t>서큐버스를 찾아서 1</t>
+  </si>
+  <si>
+    <t>서큐버스를 찾아서 2</t>
+  </si>
+  <si>
+    <t>서큐버스 처치</t>
+  </si>
+  <si>
+    <t>서고로 이동</t>
+  </si>
+  <si>
+    <t>list_map_65</t>
+  </si>
+  <si>
+    <t>list_map_66</t>
+  </si>
+  <si>
+    <t>list_map_67</t>
+  </si>
+  <si>
+    <t>list_map_68</t>
+  </si>
+  <si>
+    <t>list_map_69</t>
+  </si>
+  <si>
+    <t>list_map_70</t>
+  </si>
+  <si>
+    <t>list_map_71</t>
+  </si>
+  <si>
+    <t>list_map_72</t>
+  </si>
+  <si>
+    <t>list_map_73</t>
+  </si>
+  <si>
+    <t>list_map_74</t>
+  </si>
+  <si>
+    <t>list_map_75</t>
+  </si>
+  <si>
+    <t>list_map_76</t>
+  </si>
+  <si>
+    <t>list_map_77</t>
+  </si>
+  <si>
+    <t>list_map_78</t>
+  </si>
+  <si>
+    <t>list_map_79</t>
+  </si>
+  <si>
+    <t>list_map_80</t>
+  </si>
+  <si>
+    <t>map_s4_012</t>
+  </si>
+  <si>
+    <t>map_s4_013</t>
+  </si>
+  <si>
+    <t>map_s4_014</t>
+  </si>
+  <si>
+    <t>map_s4_015</t>
+  </si>
+  <si>
+    <t>map_s4_016</t>
+  </si>
+  <si>
+    <t>map_s4_017</t>
+  </si>
+  <si>
+    <t>map_s4_018</t>
+  </si>
+  <si>
+    <t>map_s4_019</t>
+  </si>
+  <si>
+    <t>map_s4_020</t>
+  </si>
+  <si>
+    <t>map_s4_021</t>
+  </si>
+  <si>
+    <t>map_s4_022</t>
+  </si>
+  <si>
+    <t>map_s4_023</t>
+  </si>
+  <si>
+    <t>map_s4_024</t>
+  </si>
+  <si>
+    <t>map_s4_025</t>
+  </si>
+  <si>
+    <t>map_s4_026</t>
+  </si>
+  <si>
+    <t>map_s4_027</t>
+  </si>
+  <si>
+    <t>단서</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>리비이의 서</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -4349,7 +4495,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:J66"/>
+  <dimension ref="A1:J81"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.5" style="35" bestFit="1" customWidth="1"/>
@@ -6446,7 +6592,516 @@
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="F66" s="32"/>
+      <c r="A66" s="32">
+        <v>65</v>
+      </c>
+      <c r="B66" s="35" t="s">
+        <v>250</v>
+      </c>
+      <c r="C66" s="32" t="s">
+        <v>264</v>
+      </c>
+      <c r="D66" s="32" t="s">
+        <v>280</v>
+      </c>
+      <c r="E66" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="F66" s="32">
+        <v>50063</v>
+      </c>
+      <c r="G66" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="H66" s="32">
+        <v>0</v>
+      </c>
+      <c r="I66" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="J66" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A67" s="32">
+        <v>66</v>
+      </c>
+      <c r="B67" s="35" t="s">
+        <v>251</v>
+      </c>
+      <c r="C67" s="32" t="s">
+        <v>265</v>
+      </c>
+      <c r="D67" s="32" t="s">
+        <v>281</v>
+      </c>
+      <c r="E67" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="F67" s="35">
+        <v>50064</v>
+      </c>
+      <c r="G67" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="H67" s="32">
+        <v>0</v>
+      </c>
+      <c r="I67" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="J67" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A68" s="32">
+        <v>67</v>
+      </c>
+      <c r="B68" s="35" t="s">
+        <v>252</v>
+      </c>
+      <c r="C68" s="32" t="s">
+        <v>266</v>
+      </c>
+      <c r="D68" s="32" t="s">
+        <v>282</v>
+      </c>
+      <c r="E68" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="F68" s="35">
+        <v>50065</v>
+      </c>
+      <c r="G68" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="H68" s="32">
+        <v>0</v>
+      </c>
+      <c r="I68" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="J68" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A69" s="32">
+        <v>68</v>
+      </c>
+      <c r="B69" s="35" t="s">
+        <v>253</v>
+      </c>
+      <c r="C69" s="32" t="s">
+        <v>267</v>
+      </c>
+      <c r="D69" s="32" t="s">
+        <v>283</v>
+      </c>
+      <c r="E69" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="F69" s="35">
+        <v>50066</v>
+      </c>
+      <c r="G69" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="H69" s="32">
+        <v>0</v>
+      </c>
+      <c r="I69" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="J69" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A70" s="32">
+        <v>69</v>
+      </c>
+      <c r="B70" s="35" t="s">
+        <v>254</v>
+      </c>
+      <c r="C70" s="32" t="s">
+        <v>268</v>
+      </c>
+      <c r="D70" s="32" t="s">
+        <v>284</v>
+      </c>
+      <c r="E70" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="F70" s="35">
+        <v>50067</v>
+      </c>
+      <c r="G70" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="H70" s="32">
+        <v>0</v>
+      </c>
+      <c r="I70" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="J70" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A71" s="32">
+        <v>70</v>
+      </c>
+      <c r="B71" s="35" t="s">
+        <v>255</v>
+      </c>
+      <c r="C71" s="32" t="s">
+        <v>269</v>
+      </c>
+      <c r="D71" s="32" t="s">
+        <v>285</v>
+      </c>
+      <c r="E71" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="F71" s="35">
+        <v>50068</v>
+      </c>
+      <c r="G71" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="H71" s="32">
+        <v>0</v>
+      </c>
+      <c r="I71" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="J71" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A72" s="32">
+        <v>71</v>
+      </c>
+      <c r="B72" s="35" t="s">
+        <v>256</v>
+      </c>
+      <c r="C72" s="32" t="s">
+        <v>270</v>
+      </c>
+      <c r="D72" s="32" t="s">
+        <v>286</v>
+      </c>
+      <c r="E72" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="F72" s="35">
+        <v>50069</v>
+      </c>
+      <c r="G72" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="H72" s="32">
+        <v>0</v>
+      </c>
+      <c r="I72" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="J72" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A73" s="32">
+        <v>72</v>
+      </c>
+      <c r="B73" s="35" t="s">
+        <v>257</v>
+      </c>
+      <c r="C73" s="32" t="s">
+        <v>271</v>
+      </c>
+      <c r="D73" s="32" t="s">
+        <v>287</v>
+      </c>
+      <c r="E73" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="F73" s="35">
+        <v>50070</v>
+      </c>
+      <c r="G73" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="H73" s="32">
+        <v>0</v>
+      </c>
+      <c r="I73" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="J73" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A74" s="32">
+        <v>73</v>
+      </c>
+      <c r="B74" s="35" t="s">
+        <v>258</v>
+      </c>
+      <c r="C74" s="32" t="s">
+        <v>272</v>
+      </c>
+      <c r="D74" s="32" t="s">
+        <v>288</v>
+      </c>
+      <c r="E74" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="F74" s="35">
+        <v>50071</v>
+      </c>
+      <c r="G74" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="H74" s="32">
+        <v>0</v>
+      </c>
+      <c r="I74" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="J74" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A75" s="32">
+        <v>74</v>
+      </c>
+      <c r="B75" s="35" t="s">
+        <v>259</v>
+      </c>
+      <c r="C75" s="32" t="s">
+        <v>273</v>
+      </c>
+      <c r="D75" s="32" t="s">
+        <v>289</v>
+      </c>
+      <c r="E75" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="F75" s="35">
+        <v>50072</v>
+      </c>
+      <c r="G75" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="H75" s="32">
+        <v>0</v>
+      </c>
+      <c r="I75" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="J75" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A76" s="32">
+        <v>75</v>
+      </c>
+      <c r="B76" s="35" t="s">
+        <v>260</v>
+      </c>
+      <c r="C76" s="32" t="s">
+        <v>274</v>
+      </c>
+      <c r="D76" s="32" t="s">
+        <v>290</v>
+      </c>
+      <c r="E76" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="F76" s="35">
+        <v>50073</v>
+      </c>
+      <c r="G76" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="H76" s="32">
+        <v>0</v>
+      </c>
+      <c r="I76" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="J76" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A77" s="32">
+        <v>76</v>
+      </c>
+      <c r="B77" s="35" t="s">
+        <v>261</v>
+      </c>
+      <c r="C77" s="32" t="s">
+        <v>275</v>
+      </c>
+      <c r="D77" s="32" t="s">
+        <v>291</v>
+      </c>
+      <c r="E77" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="F77" s="35">
+        <v>50074</v>
+      </c>
+      <c r="G77" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="H77" s="32">
+        <v>0</v>
+      </c>
+      <c r="I77" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="J77" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A78" s="32">
+        <v>77</v>
+      </c>
+      <c r="B78" s="35" t="s">
+        <v>262</v>
+      </c>
+      <c r="C78" s="32" t="s">
+        <v>276</v>
+      </c>
+      <c r="D78" s="32" t="s">
+        <v>292</v>
+      </c>
+      <c r="E78" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="F78" s="35">
+        <v>50075</v>
+      </c>
+      <c r="G78" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="H78" s="32">
+        <v>0</v>
+      </c>
+      <c r="I78" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="J78" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A79" s="32">
+        <v>78</v>
+      </c>
+      <c r="B79" s="35" t="s">
+        <v>263</v>
+      </c>
+      <c r="C79" s="32" t="s">
+        <v>277</v>
+      </c>
+      <c r="D79" s="32" t="s">
+        <v>293</v>
+      </c>
+      <c r="E79" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="F79" s="35">
+        <v>50076</v>
+      </c>
+      <c r="G79" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="H79" s="32">
+        <v>0</v>
+      </c>
+      <c r="I79" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="J79" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A80" s="32">
+        <v>79</v>
+      </c>
+      <c r="B80" s="35" t="s">
+        <v>296</v>
+      </c>
+      <c r="C80" s="32" t="s">
+        <v>278</v>
+      </c>
+      <c r="D80" s="32" t="s">
+        <v>294</v>
+      </c>
+      <c r="E80" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="F80" s="35">
+        <v>50077</v>
+      </c>
+      <c r="G80" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="H80" s="32">
+        <v>0</v>
+      </c>
+      <c r="I80" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="J80" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A81" s="32">
+        <v>80</v>
+      </c>
+      <c r="B81" s="35" t="s">
+        <v>297</v>
+      </c>
+      <c r="C81" s="32" t="s">
+        <v>279</v>
+      </c>
+      <c r="D81" s="32" t="s">
+        <v>295</v>
+      </c>
+      <c r="E81" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="F81" s="35">
+        <v>50078</v>
+      </c>
+      <c r="G81" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="H81" s="32">
+        <v>0</v>
+      </c>
+      <c r="I81" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="J81" s="32">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H2"/>

--- a/30_table/01_테스트버전/Table_List_Map.xlsx
+++ b/30_table/01_테스트버전/Table_List_Map.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="302">
   <si>
     <t>작업자</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -989,6 +989,22 @@
   </si>
   <si>
     <t>리비이의 서</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음 맵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Next_Map</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>클리어 했을 때 다음 맵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Next_Map</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3539,7 +3555,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:P44"/>
+  <dimension ref="A1:P45"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.75" style="24" customWidth="1"/>
@@ -3855,15 +3871,31 @@
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
     </row>
-    <row r="10" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="21"/>
-      <c r="B10" s="22"/>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="22"/>
-      <c r="H10" s="7"/>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A10" s="19">
+        <v>9</v>
+      </c>
+      <c r="B10" s="25" t="s">
+        <v>298</v>
+      </c>
+      <c r="C10" s="25" t="s">
+        <v>299</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" s="20">
+        <v>0</v>
+      </c>
+      <c r="G10" s="20">
+        <v>32</v>
+      </c>
+      <c r="H10" s="26" t="s">
+        <v>300</v>
+      </c>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
@@ -3873,15 +3905,15 @@
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A11" s="23"/>
-      <c r="B11" s="23"/>
-      <c r="C11" s="23"/>
-      <c r="D11" s="23"/>
-      <c r="E11" s="23"/>
-      <c r="F11" s="23"/>
-      <c r="G11" s="23"/>
-      <c r="H11" s="1"/>
+    <row r="11" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="21"/>
+      <c r="B11" s="22"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="22"/>
+      <c r="F11" s="22"/>
+      <c r="G11" s="22"/>
+      <c r="H11" s="7"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
@@ -4485,6 +4517,24 @@
       <c r="O44" s="1"/>
       <c r="P44" s="1"/>
     </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A45" s="23"/>
+      <c r="B45" s="23"/>
+      <c r="C45" s="23"/>
+      <c r="D45" s="23"/>
+      <c r="E45" s="23"/>
+      <c r="F45" s="23"/>
+      <c r="G45" s="23"/>
+      <c r="H45" s="1"/>
+      <c r="I45" s="1"/>
+      <c r="J45" s="1"/>
+      <c r="K45" s="1"/>
+      <c r="L45" s="1"/>
+      <c r="M45" s="1"/>
+      <c r="N45" s="1"/>
+      <c r="O45" s="1"/>
+      <c r="P45" s="1"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4495,7 +4545,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:J81"/>
+  <dimension ref="A1:K81"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.5" style="35" bestFit="1" customWidth="1"/>
@@ -4511,7 +4561,7 @@
     <col min="11" max="16384" width="9" style="31"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="28" t="s">
         <v>16</v>
       </c>
@@ -4542,8 +4592,11 @@
       <c r="J1" s="30" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K1" s="30" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="32">
         <v>1</v>
       </c>
@@ -4574,8 +4627,9 @@
       <c r="J2" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K2" s="32"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="32">
         <v>2</v>
       </c>
@@ -4606,8 +4660,9 @@
       <c r="J3" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K3" s="32"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="32">
         <v>3</v>
       </c>
@@ -4638,8 +4693,9 @@
       <c r="J4" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K4" s="32"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="32">
         <v>4</v>
       </c>
@@ -4670,8 +4726,9 @@
       <c r="J5" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K5" s="32"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="32">
         <v>5</v>
       </c>
@@ -4702,8 +4759,9 @@
       <c r="J6" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K6" s="32"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="32">
         <v>6</v>
       </c>
@@ -4734,8 +4792,9 @@
       <c r="J7" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K7" s="32"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="32">
         <v>7</v>
       </c>
@@ -4766,8 +4825,9 @@
       <c r="J8" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K8" s="32"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="32">
         <v>8</v>
       </c>
@@ -4798,8 +4858,9 @@
       <c r="J9" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K9" s="32"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="32">
         <v>9</v>
       </c>
@@ -4830,8 +4891,9 @@
       <c r="J10" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K10" s="32"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="32">
         <v>10</v>
       </c>
@@ -4862,8 +4924,9 @@
       <c r="J11" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K11" s="32"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="32">
         <v>11</v>
       </c>
@@ -4894,8 +4957,9 @@
       <c r="J12" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K12" s="32"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="32">
         <v>12</v>
       </c>
@@ -4926,8 +4990,9 @@
       <c r="J13" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K13" s="32"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="32">
         <v>13</v>
       </c>
@@ -4958,8 +5023,9 @@
       <c r="J14" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K14" s="32"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="32">
         <v>14</v>
       </c>
@@ -4990,8 +5056,9 @@
       <c r="J15" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K15" s="32"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="32">
         <v>15</v>
       </c>
@@ -5022,8 +5089,9 @@
       <c r="J16" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K16" s="32"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="32">
         <v>16</v>
       </c>
@@ -5054,8 +5122,9 @@
       <c r="J17" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K17" s="32"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="32">
         <v>17</v>
       </c>
@@ -5086,8 +5155,9 @@
       <c r="J18" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K18" s="32"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="32">
         <v>18</v>
       </c>
@@ -5118,8 +5188,9 @@
       <c r="J19" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K19" s="32"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="32">
         <v>19</v>
       </c>
@@ -5150,8 +5221,9 @@
       <c r="J20" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K20" s="32"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="32">
         <v>20</v>
       </c>
@@ -5182,8 +5254,9 @@
       <c r="J21" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K21" s="32"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="32">
         <v>21</v>
       </c>
@@ -5214,8 +5287,9 @@
       <c r="J22" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K22" s="32"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="32">
         <v>22</v>
       </c>
@@ -5246,8 +5320,9 @@
       <c r="J23" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K23" s="32"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="32">
         <v>23</v>
       </c>
@@ -5278,8 +5353,9 @@
       <c r="J24" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K24" s="32"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="32">
         <v>24</v>
       </c>
@@ -5310,8 +5386,9 @@
       <c r="J25" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K25" s="32"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="32">
         <v>25</v>
       </c>
@@ -5342,8 +5419,9 @@
       <c r="J26" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K26" s="35"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="32">
         <v>26</v>
       </c>
@@ -5374,8 +5452,9 @@
       <c r="J27" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K27" s="35"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="32">
         <v>27</v>
       </c>
@@ -5406,8 +5485,9 @@
       <c r="J28" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K28" s="35"/>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="32">
         <v>28</v>
       </c>
@@ -5438,8 +5518,9 @@
       <c r="J29" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K29" s="35"/>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" s="32">
         <v>29</v>
       </c>
@@ -5470,8 +5551,9 @@
       <c r="J30" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K30" s="35"/>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" s="32">
         <v>30</v>
       </c>
@@ -5502,8 +5584,9 @@
       <c r="J31" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K31" s="35"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" s="32">
         <v>31</v>
       </c>
@@ -5534,8 +5617,9 @@
       <c r="J32" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K32" s="35"/>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" s="32">
         <v>32</v>
       </c>
@@ -5566,8 +5650,9 @@
       <c r="J33" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K33" s="35"/>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" s="32">
         <v>33</v>
       </c>
@@ -5598,8 +5683,9 @@
       <c r="J34" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K34" s="35"/>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" s="32">
         <v>34</v>
       </c>
@@ -5630,8 +5716,9 @@
       <c r="J35" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K35" s="35"/>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" s="32">
         <v>35</v>
       </c>
@@ -5662,8 +5749,9 @@
       <c r="J36" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K36" s="35"/>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" s="32">
         <v>36</v>
       </c>
@@ -5694,8 +5782,9 @@
       <c r="J37" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K37" s="35"/>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" s="32">
         <v>37</v>
       </c>
@@ -5726,8 +5815,9 @@
       <c r="J38" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K38" s="35"/>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" s="32">
         <v>38</v>
       </c>
@@ -5758,8 +5848,9 @@
       <c r="J39" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K39" s="35"/>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" s="32">
         <v>39</v>
       </c>
@@ -5790,8 +5881,9 @@
       <c r="J40" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K40" s="35"/>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" s="32">
         <v>40</v>
       </c>
@@ -5822,8 +5914,9 @@
       <c r="J41" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K41" s="35"/>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" s="32">
         <v>41</v>
       </c>
@@ -5854,8 +5947,9 @@
       <c r="J42" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K42" s="35"/>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" s="32">
         <v>42</v>
       </c>
@@ -5886,8 +5980,9 @@
       <c r="J43" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K43" s="35"/>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" s="32">
         <v>43</v>
       </c>
@@ -5918,8 +6013,9 @@
       <c r="J44" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K44" s="35"/>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" s="32">
         <v>44</v>
       </c>
@@ -5950,8 +6046,9 @@
       <c r="J45" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K45" s="35"/>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" s="32">
         <v>45</v>
       </c>
@@ -5982,8 +6079,9 @@
       <c r="J46" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K46" s="35"/>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" s="32">
         <v>46</v>
       </c>
@@ -6014,8 +6112,9 @@
       <c r="J47" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K47" s="35"/>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" s="32">
         <v>47</v>
       </c>
@@ -6046,8 +6145,9 @@
       <c r="J48" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K48" s="35"/>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" s="32">
         <v>48</v>
       </c>
@@ -6078,8 +6178,9 @@
       <c r="J49" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K49" s="35"/>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" s="32">
         <v>49</v>
       </c>
@@ -6110,8 +6211,9 @@
       <c r="J50" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K50" s="35"/>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" s="32">
         <v>50</v>
       </c>
@@ -6142,8 +6244,9 @@
       <c r="J51" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K51" s="35"/>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52" s="32">
         <v>51</v>
       </c>
@@ -6174,8 +6277,9 @@
       <c r="J52" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K52" s="35"/>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" s="32">
         <v>52</v>
       </c>
@@ -6206,8 +6310,9 @@
       <c r="J53" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K53" s="35"/>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" s="32">
         <v>53</v>
       </c>
@@ -6238,8 +6343,9 @@
       <c r="J54" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K54" s="35"/>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55" s="32">
         <v>54</v>
       </c>
@@ -6270,8 +6376,9 @@
       <c r="J55" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K55" s="32"/>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56" s="32">
         <v>55</v>
       </c>
@@ -6302,8 +6409,9 @@
       <c r="J56" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K56" s="32"/>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57" s="32">
         <v>56</v>
       </c>
@@ -6334,8 +6442,9 @@
       <c r="J57" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K57" s="32"/>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58" s="32">
         <v>57</v>
       </c>
@@ -6366,8 +6475,9 @@
       <c r="J58" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K58" s="32"/>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" s="32">
         <v>58</v>
       </c>
@@ -6398,8 +6508,9 @@
       <c r="J59" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K59" s="32"/>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60" s="32">
         <v>59</v>
       </c>
@@ -6430,8 +6541,9 @@
       <c r="J60" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K60" s="32"/>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61" s="32">
         <v>60</v>
       </c>
@@ -6462,8 +6574,9 @@
       <c r="J61" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K61" s="32"/>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62" s="32">
         <v>61</v>
       </c>
@@ -6494,8 +6607,9 @@
       <c r="J62" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K62" s="32"/>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63" s="32">
         <v>62</v>
       </c>
@@ -6526,8 +6640,9 @@
       <c r="J63" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K63" s="32"/>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64" s="32">
         <v>63</v>
       </c>
@@ -6558,8 +6673,9 @@
       <c r="J64" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K64" s="32"/>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65" s="32">
         <v>64</v>
       </c>
@@ -6590,8 +6706,9 @@
       <c r="J65" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K65" s="32"/>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66" s="32">
         <v>65</v>
       </c>
@@ -6622,8 +6739,9 @@
       <c r="J66" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K66" s="32"/>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67" s="32">
         <v>66</v>
       </c>
@@ -6654,8 +6772,9 @@
       <c r="J67" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K67" s="32"/>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68" s="32">
         <v>67</v>
       </c>
@@ -6686,8 +6805,9 @@
       <c r="J68" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K68" s="32"/>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69" s="32">
         <v>68</v>
       </c>
@@ -6718,8 +6838,9 @@
       <c r="J69" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K69" s="32"/>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70" s="32">
         <v>69</v>
       </c>
@@ -6750,8 +6871,9 @@
       <c r="J70" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K70" s="32"/>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71" s="32">
         <v>70</v>
       </c>
@@ -6782,8 +6904,9 @@
       <c r="J71" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K71" s="32"/>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72" s="32">
         <v>71</v>
       </c>
@@ -6814,8 +6937,9 @@
       <c r="J72" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K72" s="32"/>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73" s="32">
         <v>72</v>
       </c>
@@ -6846,8 +6970,9 @@
       <c r="J73" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K73" s="32"/>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74" s="32">
         <v>73</v>
       </c>
@@ -6878,8 +7003,9 @@
       <c r="J74" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K74" s="32"/>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A75" s="32">
         <v>74</v>
       </c>
@@ -6910,8 +7036,9 @@
       <c r="J75" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K75" s="32"/>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76" s="32">
         <v>75</v>
       </c>
@@ -6942,8 +7069,9 @@
       <c r="J76" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K76" s="32"/>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A77" s="32">
         <v>76</v>
       </c>
@@ -6974,8 +7102,9 @@
       <c r="J77" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K77" s="32"/>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A78" s="32">
         <v>77</v>
       </c>
@@ -7006,8 +7135,9 @@
       <c r="J78" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K78" s="32"/>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A79" s="32">
         <v>78</v>
       </c>
@@ -7038,8 +7168,9 @@
       <c r="J79" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K79" s="32"/>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A80" s="32">
         <v>79</v>
       </c>
@@ -7070,8 +7201,9 @@
       <c r="J80" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K80" s="32"/>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A81" s="32">
         <v>80</v>
       </c>
@@ -7102,6 +7234,7 @@
       <c r="J81" s="32">
         <v>0</v>
       </c>
+      <c r="K81" s="32"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:H2"/>

--- a/30_table/01_테스트버전/Table_List_Map.xlsx
+++ b/30_table/01_테스트버전/Table_List_Map.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="305">
   <si>
     <t>작업자</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1005,6 +1005,17 @@
   </si>
   <si>
     <t>Next_Map</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>만든 사람들</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>list_map_81</t>
+  </si>
+  <si>
+    <t>map_s0_001</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4545,7 +4556,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:K81"/>
+  <dimension ref="A1:K82"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.5" style="35" bestFit="1" customWidth="1"/>
@@ -7236,6 +7247,39 @@
       </c>
       <c r="K81" s="32"/>
     </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A82" s="32">
+        <v>81</v>
+      </c>
+      <c r="B82" s="35" t="s">
+        <v>302</v>
+      </c>
+      <c r="C82" s="32" t="s">
+        <v>303</v>
+      </c>
+      <c r="D82" s="35" t="s">
+        <v>304</v>
+      </c>
+      <c r="E82" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="F82" s="35">
+        <v>0</v>
+      </c>
+      <c r="G82" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="H82" s="32">
+        <v>0</v>
+      </c>
+      <c r="I82" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="J82" s="32">
+        <v>0</v>
+      </c>
+      <c r="K82" s="35"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H2"/>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -7248,7 +7292,7 @@
           <x14:formula1>
             <xm:f>Type!$A$2:$A$101</xm:f>
           </x14:formula1>
-          <xm:sqref>E2:E1048576 I2:I1048576 G2:G1048576</xm:sqref>
+          <xm:sqref>G2:G1048576 I2:I1048576 E2:E1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
